--- a/data/trans_camb/IP41-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 1,34</t>
+          <t>-8,34; 0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,24; -4,74</t>
+          <t>-17,42; -5,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-97,67; -91,54</t>
+          <t>-97,61; -91,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -1,15</t>
+          <t>-11,81; -1,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 2,25</t>
+          <t>-7,27; 2,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-97,0; -90,95</t>
+          <t>-96,87; -90,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; -0,94</t>
+          <t>-8,34; -1,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,53; -2,84</t>
+          <t>-10,65; -2,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-96,66; -92,44</t>
+          <t>-96,78; -92,52</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 1,46</t>
+          <t>-8,68; 1,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -5,14</t>
+          <t>-17,96; -5,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -1,26</t>
+          <t>-12,3; -1,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 2,38</t>
+          <t>-7,53; 2,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -1,03</t>
+          <t>-8,75; -1,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,93; -3,02</t>
+          <t>-11,09; -2,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 2,27</t>
+          <t>-6,9; 1,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; -1,68</t>
+          <t>-11,0; -1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-94,75; -88,43</t>
+          <t>-94,52; -88,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 1,48</t>
+          <t>-6,68; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -5,73</t>
+          <t>-15,46; -5,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-96,64; -91,46</t>
+          <t>-96,66; -91,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,25</t>
+          <t>-5,77; 0,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,65; -5,04</t>
+          <t>-11,76; -5,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-94,81; -91,05</t>
+          <t>-95,09; -91,21</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 2,62</t>
+          <t>-7,41; 1,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,98; -1,93</t>
+          <t>-11,88; -1,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 1,55</t>
+          <t>-6,98; 1,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,62; -6,13</t>
+          <t>-16,18; -6,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,28</t>
+          <t>-6,08; 0,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -5,47</t>
+          <t>-12,44; -5,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 3,03</t>
+          <t>-7,19; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -2,22</t>
+          <t>-14,19; -2,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-94,78; -87,46</t>
+          <t>-95,07; -87,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 0,23</t>
+          <t>-9,78; 0,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,76; -8,06</t>
+          <t>-20,5; -8,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-95,47; -88,75</t>
+          <t>-95,62; -89,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 0,22</t>
+          <t>-7,11; 0,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -6,81</t>
+          <t>-15,44; -6,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-94,44; -89,5</t>
+          <t>-94,4; -89,17</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 3,34</t>
+          <t>-7,63; 3,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -2,32</t>
+          <t>-15,14; -2,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 0,33</t>
+          <t>-10,23; 0,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -9,04</t>
+          <t>-21,58; -9,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 0,24</t>
+          <t>-7,57; 0,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -7,47</t>
+          <t>-16,52; -7,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 5,22</t>
+          <t>-6,05; 4,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 1,72</t>
+          <t>-10,6; 2,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-90,35; -82,22</t>
+          <t>-90,51; -82,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 2,09</t>
+          <t>-10,03; 1,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,09; -1,75</t>
+          <t>-13,28; -1,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-91,76; -84,63</t>
+          <t>-92,02; -84,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 1,88</t>
+          <t>-6,36; 1,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,78; -1,31</t>
+          <t>-10,03; -1,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-90,28; -85,0</t>
+          <t>-90,31; -84,94</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 6,27</t>
+          <t>-6,8; 5,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 1,87</t>
+          <t>-11,68; 3,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 2,42</t>
+          <t>-11,04; 1,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -2,11</t>
+          <t>-14,6; -1,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 2,17</t>
+          <t>-7,14; 2,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,02; -1,6</t>
+          <t>-11,21; -1,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,7</t>
+          <t>-4,45; 0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,74; -3,9</t>
+          <t>-10,16; -4,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-92,76; -89,19</t>
+          <t>-92,77; -89,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -1,64</t>
+          <t>-6,67; -1,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -5,66</t>
+          <t>-11,36; -5,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-93,89; -90,54</t>
+          <t>-93,81; -90,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,49</t>
+          <t>-4,98; -1,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -5,87</t>
+          <t>-9,73; -5,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-92,95; -90,5</t>
+          <t>-92,92; -90,55</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,77</t>
+          <t>-4,85; 0,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,58; -4,37</t>
+          <t>-11,04; -4,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -1,83</t>
+          <t>-7,12; -1,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -6,19</t>
+          <t>-12,27; -6,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -1,64</t>
+          <t>-5,36; -1,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -6,43</t>
+          <t>-10,44; -6,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">

--- a/data/trans_camb/IP41-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Habitat-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-95,2</t>
+          <t>-6,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-4,87</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-94,54</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-4,87</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>-6,52</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-94,85</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 0,95</t>
+          <t>-8,48; 1,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,42; -5,44</t>
+          <t>-17,33; -5,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-97,61; -91,86</t>
+          <t>-11,3; -1,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -1,3</t>
+          <t>-7,38; 2,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 2,3</t>
+          <t>-8,33; -1,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-96,87; -90,61</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-8,34; -1,3</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-10,65; -2,76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-96,78; -92,52</t>
+          <t>-11,01; -3,11</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-6,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,7%</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-2,66%</t>
+          <t>-5,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-5,13%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>-6,87%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 1,0</t>
+          <t>-8,75; 1,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,96; -5,78</t>
+          <t>-18,22; -5,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,81; -1,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,3; -1,41</t>
+          <t>-7,69; 2,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 2,49</t>
+          <t>-8,71; -1,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-8,75; -1,37</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-11,09; -2,97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-11,37; -3,32</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-91,94</t>
+          <t>-2,58</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,58</t>
+          <t>-10,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-10,05</t>
+          <t>-2,57</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-94,45</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-2,57</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>-8,21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-93,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 1,69</t>
+          <t>-7,12; 1,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -1,27</t>
+          <t>-11,29; -1,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-94,52; -88,29</t>
+          <t>-6,5; 1,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 0,98</t>
+          <t>-14,65; -5,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,79</t>
+          <t>-5,73; 0,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-96,66; -91,66</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-5,77; 0,57</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-11,76; -5,0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-95,09; -91,21</t>
+          <t>-11,86; -5,12</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-2,73%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,73%</t>
+          <t>-10,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-10,65%</t>
+          <t>-2,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>-8,81%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 1,95</t>
+          <t>-7,56; 1,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -1,45</t>
+          <t>-12,05; -1,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,82; 1,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,06</t>
+          <t>-15,25; -6,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,18; -6,22</t>
+          <t>-6,15; 0,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-6,08; 0,61</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-12,44; -5,44</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-12,58; -5,56</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-91,94</t>
+          <t>-4,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>-14,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-14,05</t>
+          <t>-3,44</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-92,57</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,44</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>-11,05</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-92,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 2,8</t>
+          <t>-6,92; 3,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,19; -2,32</t>
+          <t>-13,22; -2,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-95,07; -87,84</t>
+          <t>-10,11; 0,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 0,86</t>
+          <t>-21,04; -8,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,5; -8,41</t>
+          <t>-7,01; -0,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-95,62; -89,0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-7,11; 0,26</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-15,44; -6,87</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-94,4; -89,17</t>
+          <t>-15,54; -7,02</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-5,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,05%</t>
+          <t>-15,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-15,18%</t>
+          <t>-3,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-3,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>-11,97%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 3,1</t>
+          <t>-7,37; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -2,7</t>
+          <t>-14,13; -2,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,74; 0,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 0,98</t>
+          <t>-22,39; -9,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,58; -9,32</t>
+          <t>-7,44; -0,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-7,57; 0,28</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-16,52; -7,69</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-16,5; -7,58</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-87,0</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-7,21</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-7,21</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-88,52</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-2,05</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>-5,76</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-87,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 4,94</t>
+          <t>-5,86; 5,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 2,51</t>
+          <t>-10,17; 1,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-90,51; -82,78</t>
+          <t>-9,83; 1,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 1,08</t>
+          <t>-12,49; -1,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,28; -1,58</t>
+          <t>-6,35; 1,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-92,02; -84,61</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-6,36; 1,89</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-10,03; -1,62</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-90,31; -84,94</t>
+          <t>-10,27; -1,87</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,21%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,21%</t>
+          <t>-8,15%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-8,15%</t>
+          <t>-2,33%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-2,33%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>-6,56%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 5,9</t>
+          <t>-6,43; 6,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 3,04</t>
+          <t>-11,31; 1,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,83; 1,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 1,21</t>
+          <t>-13,85; -1,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -1,83</t>
+          <t>-7,14; 2,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-7,14; 2,22</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-11,21; -1,89</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-11,51; -2,18</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1227,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-91,09</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-8,63</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-92,38</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
           <t>-7,79</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-91,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,57</t>
+          <t>-4,54; 0,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -4,17</t>
+          <t>-9,95; -4,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-92,77; -89,27</t>
+          <t>-6,67; -1,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -1,7</t>
+          <t>-11,45; -6,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -5,84</t>
+          <t>-4,9; -1,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-93,81; -90,74</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; -1,38</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-9,73; -5,93</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-92,92; -90,55</t>
+          <t>-9,85; -5,86</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1303,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,44%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-4,44%</t>
+          <t>-9,34%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-9,34%</t>
+          <t>-3,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-3,32%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
           <t>-8,49%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,63</t>
+          <t>-4,92; 0,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -4,66</t>
+          <t>-10,78; -4,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,15; -2,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -1,88</t>
+          <t>-12,24; -6,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -6,45</t>
+          <t>-5,32; -1,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; -1,51</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-10,44; -6,47</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,67; -6,47</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1370,11 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>

--- a/data/trans_camb/IP41-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-6,34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,51</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-3,24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-10,96</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 1,48</t>
+          <t>-11,49; -1,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -5,13</t>
+          <t>-7,5; 2,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,3; -1,13</t>
+          <t>-8,4; 1,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 2,21</t>
+          <t>-17,24; -4,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -1,44</t>
+          <t>-8,22; -0,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,01; -3,11</t>
+          <t>-10,53; -2,84</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-6,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-2,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-3,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-11,51%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-6,7%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,57</t>
+          <t>-12,05; -1,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -5,53</t>
+          <t>-7,82; 2,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -1,23</t>
+          <t>-8,73; 1,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 2,37</t>
+          <t>-18,09; -5,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -1,56</t>
+          <t>-8,6; -1,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,37; -3,32</t>
+          <t>-10,93; -3,02</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,58</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-10,05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-2,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-6,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-10,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 1,61</t>
+          <t>-6,41; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -1,05</t>
+          <t>-14,98; -5,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 1,34</t>
+          <t>-6,89; 2,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -5,73</t>
+          <t>-11,31; -1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 0,21</t>
+          <t>-5,57; 0,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,86; -5,12</t>
+          <t>-11,65; -5,04</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-2,73%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-10,65%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-2,79%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-6,76%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,73%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 1,84</t>
+          <t>-6,72; 1,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -1,16</t>
+          <t>-15,62; -6,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 1,32</t>
+          <t>-7,36; 2,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -6,1</t>
+          <t>-11,98; -1,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 0,2</t>
+          <t>-5,9; 0,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,58; -5,56</t>
+          <t>-12,4; -5,47</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-14,05</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-2,1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-7,85</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,68</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-14,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 3,25</t>
+          <t>-10,28; 0,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -2,35</t>
+          <t>-20,76; -8,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 0,47</t>
+          <t>-7,16; 3,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,04; -8,09</t>
+          <t>-12,97; -2,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; -0,13</t>
+          <t>-7,01; 0,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,54; -7,02</t>
+          <t>-15,49; -6,81</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-5,05%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-15,18%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-2,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-8,54%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-5,05%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-15,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 3,61</t>
+          <t>-10,88; 0,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -2,67</t>
+          <t>-22,3; -9,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 0,23</t>
+          <t>-7,78; 3,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,39; -9,05</t>
+          <t>-13,72; -2,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,44; -0,13</t>
+          <t>-7,54; 0,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -7,58</t>
+          <t>-16,55; -7,47</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-7,21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-4,3</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,72</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-7,21</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 5,48</t>
+          <t>-9,24; 2,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 1,69</t>
+          <t>-13,09; -1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 1,29</t>
+          <t>-5,94; 5,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -1,02</t>
+          <t>-10,24; 1,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 1,84</t>
+          <t>-6,03; 1,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -1,87</t>
+          <t>-9,78; -1,31</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,21%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-8,15%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-0,43%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-4,95%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-4,21%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-8,15%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 6,6</t>
+          <t>-10,16; 2,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 1,99</t>
+          <t>-14,36; -2,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 1,45</t>
+          <t>-6,62; 6,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,85; -1,24</t>
+          <t>-11,63; 1,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,13</t>
+          <t>-6,73; 2,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,51; -2,18</t>
+          <t>-11,02; -1,6</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-4,1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-8,63</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-1,92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-6,9</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-8,63</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,7</t>
+          <t>-6,73; -1,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -4,04</t>
+          <t>-11,34; -5,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -1,85</t>
+          <t>-4,59; 0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -6,14</t>
+          <t>-9,74; -3,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -1,3</t>
+          <t>-5,02; -1,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -5,86</t>
+          <t>-9,82; -5,87</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,44%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-9,34%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-2,11%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-7,57%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-4,44%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-9,34%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,77</t>
+          <t>-7,27; -1,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -4,48</t>
+          <t>-12,22; -6,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -2,01</t>
+          <t>-5,01; 0,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -6,73</t>
+          <t>-10,58; -4,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -1,43</t>
+          <t>-5,4; -1,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -6,47</t>
+          <t>-10,64; -6,43</t>
         </is>
       </c>
     </row>
